--- a/src/main/resources/PotentialReviewersContact_Field_Values.xlsx
+++ b/src/main/resources/PotentialReviewersContact_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25427"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New Project\ProdLWC_Mine\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E283106-D04C-453C-ADAD-C1658347B866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA39F752-ADE8-4FB4-981A-DEC3F09D16CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{FE4041C9-411E-47B8-A648-17C164901997}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{FE4041C9-411E-47B8-A648-17C164901997}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="27">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -56,9 +56,6 @@
   </si>
   <si>
     <t>Phone</t>
-  </si>
-  <si>
-    <t>786-908-(5678)</t>
   </si>
   <si>
     <t>Contact</t>
@@ -189,9 +186,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -229,7 +226,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -335,7 +332,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -477,7 +474,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -512,7 +509,7 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -523,7 +520,7 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -534,7 +531,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -544,8 +541,8 @@
       <c r="B5" t="s">
         <v>7</v>
       </c>
-      <c r="C5" t="s">
-        <v>8</v>
+      <c r="C5">
+        <v>7869085678</v>
       </c>
     </row>
   </sheetData>
@@ -581,10 +578,10 @@
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
         <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -592,10 +589,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
         <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -603,10 +600,10 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
         <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -614,7 +611,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C5">
         <v>12345</v>
@@ -625,10 +622,10 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
         <v>19</v>
-      </c>
-      <c r="C6" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -636,10 +633,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
         <v>21</v>
-      </c>
-      <c r="C7" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -647,10 +644,10 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
         <v>23</v>
-      </c>
-      <c r="C8" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -658,10 +655,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -669,10 +666,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/PotentialReviewersContact_Field_Values.xlsx
+++ b/src/main/resources/PotentialReviewersContact_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New Project\ProdLWC_Mine\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cleanup_Projects\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA39F752-ADE8-4FB4-981A-DEC3F09D16CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97D64F05-9407-47BA-8FF0-34811A0D30A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{FE4041C9-411E-47B8-A648-17C164901997}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{FE4041C9-411E-47B8-A648-17C164901997}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -61,58 +61,58 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Automation Runtime Contact</t>
-  </si>
-  <si>
     <t>automation.sme143@yopmail.com</t>
   </si>
   <si>
-    <t>fieldExternalReviewerAddress1__c</t>
-  </si>
-  <si>
     <t>Street 1</t>
   </si>
   <si>
-    <t>fieldExternalReviewerCity__c</t>
-  </si>
-  <si>
     <t>VA</t>
   </si>
   <si>
-    <t>fieldStateDropdownList__c</t>
-  </si>
-  <si>
     <t>PA</t>
   </si>
   <si>
-    <t>fieldExternalReviewerZipCode__c</t>
-  </si>
-  <si>
-    <t>fieldAffiliatedInstitution__c</t>
-  </si>
-  <si>
     <t>Automation testing</t>
   </si>
   <si>
-    <t>fieldExternalReviewerEducation__c</t>
-  </si>
-  <si>
     <t>Automation Engineer</t>
   </si>
   <si>
-    <t>fieldExternalReviewerProfileDescription__c</t>
-  </si>
-  <si>
     <t>Test</t>
   </si>
   <si>
-    <t>fieldPrimaryAreaOfExpertisePicklist__c</t>
-  </si>
-  <si>
     <t>Ambulatory Care Programs</t>
   </si>
   <si>
-    <t>fieldPrimaryAreaOfExpertise__c</t>
+    <t>Automation Runtime</t>
+  </si>
+  <si>
+    <t>ExternalReviewerAddress1__c</t>
+  </si>
+  <si>
+    <t>ExternalReviewerCity__c</t>
+  </si>
+  <si>
+    <t>StateDropdownList__c</t>
+  </si>
+  <si>
+    <t>ExternalReviewerZipCode__c</t>
+  </si>
+  <si>
+    <t>AffiliatedInstitution__c</t>
+  </si>
+  <si>
+    <t>ExternalReviewerEducation__c</t>
+  </si>
+  <si>
+    <t>ExternalReviewerProfileDescription__c</t>
+  </si>
+  <si>
+    <t>PrimaryAreaOfExpertisePicklist__c</t>
+  </si>
+  <si>
+    <t>PrimaryAreaOfExpertise__c</t>
   </si>
 </sst>
 </file>
@@ -483,14 +483,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72DA656C-1C51-41DB-AF9C-4CA03E90FA41}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -501,7 +501,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -509,10 +509,10 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -523,7 +523,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -531,10 +531,10 @@
         <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -542,7 +542,7 @@
         <v>7</v>
       </c>
       <c r="C5">
-        <v>7869085678</v>
+        <v>8970689059</v>
       </c>
     </row>
   </sheetData>
@@ -556,13 +556,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59E2E7FA-17F4-4778-9079-BE9B528B7489}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="44.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="44.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -573,95 +573,95 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C5">
         <v>12345</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -669,7 +669,7 @@
         <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
